--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484591_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484591_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>7.0822</v>
+        <v>6.2409</v>
       </c>
       <c r="E2" t="n">
-        <v>6.3824</v>
+        <v>6.0117</v>
       </c>
       <c r="F2" t="n">
-        <v>0.6999</v>
+        <v>0.2292</v>
       </c>
       <c r="G2" t="n">
         <v>2.3976</v>
@@ -610,13 +610,13 @@
         <v>1.2828</v>
       </c>
       <c r="S2" t="n">
-        <v>1.6847</v>
+        <v>0.8433</v>
       </c>
       <c r="T2" t="n">
-        <v>0.5468</v>
+        <v>0.1761</v>
       </c>
       <c r="U2" t="n">
-        <v>1.1379</v>
+        <v>0.6672</v>
       </c>
       <c r="V2" t="n">
         <v>1.9005</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>J. MATEO LAZARO</t>
+          <t>I. FRANCH RUIZ</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,67 +643,67 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.8936</v>
+        <v>5.823</v>
       </c>
       <c r="E3" t="n">
-        <v>4.2726</v>
+        <v>4.0476</v>
       </c>
       <c r="F3" t="n">
-        <v>0.621</v>
+        <v>1.7754</v>
       </c>
       <c r="G3" t="n">
-        <v>1.0313</v>
+        <v>3.8783</v>
       </c>
       <c r="H3" t="n">
-        <v>1.0154</v>
+        <v>1.6215</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0159</v>
+        <v>2.2568</v>
       </c>
       <c r="J3" t="n">
-        <v>3.146</v>
+        <v>4.155</v>
       </c>
       <c r="K3" t="n">
-        <v>2.1359</v>
+        <v>1.353</v>
       </c>
       <c r="L3" t="n">
-        <v>1.01</v>
+        <v>2.802</v>
       </c>
       <c r="M3" t="n">
-        <v>-2.1146</v>
+        <v>-0.2768</v>
       </c>
       <c r="N3" t="n">
-        <v>-1.1205</v>
+        <v>0.2685</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.9941</v>
+        <v>-0.5452</v>
       </c>
       <c r="P3" t="n">
-        <v>1.0995</v>
+        <v>2.0158</v>
       </c>
       <c r="Q3" t="n">
-        <v>-2.0158</v>
+        <v>-0.1833</v>
       </c>
       <c r="R3" t="n">
-        <v>3.1154</v>
+        <v>2.1991</v>
       </c>
       <c r="S3" t="n">
-        <v>3.0847</v>
+        <v>0.5728</v>
       </c>
       <c r="T3" t="n">
-        <v>1.5536</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="U3" t="n">
-        <v>1.5311</v>
+        <v>0.497</v>
       </c>
       <c r="V3" t="n">
-        <v>-0.3219</v>
+        <v>-0.6439</v>
       </c>
       <c r="W3" t="n">
-        <v>1.5889</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>-1.9109</v>
+        <v>-0.6439</v>
       </c>
     </row>
     <row r="4">
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>4.8854</v>
+        <v>5.0106</v>
       </c>
       <c r="E4" t="n">
-        <v>3.2665</v>
+        <v>4.0357</v>
       </c>
       <c r="F4" t="n">
-        <v>1.6189</v>
+        <v>0.9748</v>
       </c>
       <c r="G4" t="n">
         <v>3.3073</v>
@@ -766,13 +766,13 @@
         <v>2.7489</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.354</v>
+        <v>-0.2289</v>
       </c>
       <c r="T4" t="n">
-        <v>-1.7066</v>
+        <v>-0.9374</v>
       </c>
       <c r="U4" t="n">
-        <v>1.3526</v>
+        <v>0.7085</v>
       </c>
       <c r="V4" t="n">
         <v>-0.6335</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>I. FRANCH RUIZ</t>
+          <t>R. FAS MONROS</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>4.8357</v>
+        <v>4.4354</v>
       </c>
       <c r="E5" t="n">
-        <v>3.4567</v>
+        <v>2.9608</v>
       </c>
       <c r="F5" t="n">
-        <v>1.379</v>
+        <v>1.4746</v>
       </c>
       <c r="G5" t="n">
-        <v>3.8783</v>
+        <v>3.9661</v>
       </c>
       <c r="H5" t="n">
-        <v>1.6215</v>
+        <v>1.033</v>
       </c>
       <c r="I5" t="n">
-        <v>2.2568</v>
+        <v>2.9331</v>
       </c>
       <c r="J5" t="n">
-        <v>4.155</v>
+        <v>2.8047</v>
       </c>
       <c r="K5" t="n">
-        <v>1.353</v>
+        <v>0.0959</v>
       </c>
       <c r="L5" t="n">
-        <v>2.802</v>
+        <v>2.7088</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.2768</v>
+        <v>1.1614</v>
       </c>
       <c r="N5" t="n">
-        <v>0.2685</v>
+        <v>0.9371</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.5452</v>
+        <v>0.2243</v>
       </c>
       <c r="P5" t="n">
-        <v>2.0158</v>
+        <v>1.8326</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.1833</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>2.1991</v>
+        <v>1.8326</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.4145</v>
+        <v>-0.0963</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.5151</v>
+        <v>-0.1659</v>
       </c>
       <c r="U5" t="n">
-        <v>0.1006</v>
+        <v>0.0696</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.6439</v>
+        <v>-1.267</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>0.3219</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.6439</v>
+        <v>-1.5889</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>R. FAS MONROS</t>
+          <t>J. SORIANO ZORIO</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>4.4374</v>
+        <v>3.3674</v>
       </c>
       <c r="E6" t="n">
-        <v>3.2353</v>
+        <v>2.3092</v>
       </c>
       <c r="F6" t="n">
-        <v>1.2021</v>
+        <v>1.0582</v>
       </c>
       <c r="G6" t="n">
-        <v>3.9661</v>
+        <v>-2.1374</v>
       </c>
       <c r="H6" t="n">
-        <v>1.033</v>
+        <v>0.7891</v>
       </c>
       <c r="I6" t="n">
-        <v>2.9331</v>
+        <v>-2.9264</v>
       </c>
       <c r="J6" t="n">
-        <v>2.8047</v>
+        <v>-1.2212</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0959</v>
+        <v>1.1921</v>
       </c>
       <c r="L6" t="n">
-        <v>2.7088</v>
+        <v>-2.4133</v>
       </c>
       <c r="M6" t="n">
-        <v>1.1614</v>
+        <v>-0.9161</v>
       </c>
       <c r="N6" t="n">
-        <v>0.9371</v>
+        <v>-0.403</v>
       </c>
       <c r="O6" t="n">
-        <v>0.2243</v>
+        <v>-0.5131</v>
       </c>
       <c r="P6" t="n">
-        <v>1.8326</v>
+        <v>1.2828</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1.8326</v>
+        <v>1.2828</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.09429999999999999</v>
+        <v>0.1095</v>
       </c>
       <c r="T6" t="n">
-        <v>0.1086</v>
+        <v>-0.2809</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.2029</v>
+        <v>0.3904</v>
       </c>
       <c r="V6" t="n">
-        <v>-1.267</v>
+        <v>4.1125</v>
       </c>
       <c r="W6" t="n">
-        <v>0.3219</v>
+        <v>3.8113</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.5889</v>
+        <v>0.3011</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>J. SORIANO ZORIO</t>
+          <t>P. BAENA SANCHEZ</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>3.2406</v>
+        <v>2.8335</v>
       </c>
       <c r="E7" t="n">
-        <v>2.4053</v>
+        <v>-0.2034</v>
       </c>
       <c r="F7" t="n">
-        <v>0.8353</v>
+        <v>3.0369</v>
       </c>
       <c r="G7" t="n">
-        <v>-2.1374</v>
+        <v>2.1646</v>
       </c>
       <c r="H7" t="n">
-        <v>0.7891</v>
+        <v>0.0033</v>
       </c>
       <c r="I7" t="n">
-        <v>-2.9264</v>
+        <v>2.1613</v>
       </c>
       <c r="J7" t="n">
-        <v>-1.2212</v>
+        <v>1.6947</v>
       </c>
       <c r="K7" t="n">
-        <v>1.1921</v>
+        <v>-0.4026</v>
       </c>
       <c r="L7" t="n">
-        <v>-2.4133</v>
+        <v>2.0973</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.9161</v>
+        <v>0.4698</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.403</v>
+        <v>0.4059</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.5131</v>
+        <v>0.064</v>
       </c>
       <c r="P7" t="n">
-        <v>1.2828</v>
+        <v>0.9163</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-1.8326</v>
       </c>
       <c r="R7" t="n">
-        <v>1.2828</v>
+        <v>2.7489</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.0173</v>
+        <v>-0.2474</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.1847</v>
+        <v>-0.06560000000000001</v>
       </c>
       <c r="U7" t="n">
-        <v>0.1675</v>
+        <v>-0.1818</v>
       </c>
       <c r="V7" t="n">
-        <v>4.1125</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>3.8113</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>0.3011</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A. DEMBELE CUESTA</t>
+          <t>J. MATEO LAZARO</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>2.1376</v>
+        <v>2.7299</v>
       </c>
       <c r="E8" t="n">
-        <v>1.4651</v>
+        <v>2.9265</v>
       </c>
       <c r="F8" t="n">
-        <v>0.6725</v>
+        <v>-0.1966</v>
       </c>
       <c r="G8" t="n">
-        <v>0.6378</v>
+        <v>1.0313</v>
       </c>
       <c r="H8" t="n">
-        <v>0.2564</v>
+        <v>1.0154</v>
       </c>
       <c r="I8" t="n">
-        <v>0.3814</v>
+        <v>0.0159</v>
       </c>
       <c r="J8" t="n">
-        <v>0.125</v>
+        <v>3.146</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>2.1359</v>
       </c>
       <c r="L8" t="n">
-        <v>0.125</v>
+        <v>1.01</v>
       </c>
       <c r="M8" t="n">
-        <v>0.5128</v>
+        <v>-2.1146</v>
       </c>
       <c r="N8" t="n">
-        <v>0.2564</v>
+        <v>-1.1205</v>
       </c>
       <c r="O8" t="n">
-        <v>0.2564</v>
+        <v>-0.9941</v>
       </c>
       <c r="P8" t="n">
-        <v>0.3665</v>
+        <v>1.0995</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>-2.0158</v>
       </c>
       <c r="R8" t="n">
-        <v>0.3665</v>
+        <v>3.1154</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.1337</v>
+        <v>0.921</v>
       </c>
       <c r="T8" t="n">
-        <v>0.0732</v>
+        <v>0.2074</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.2069</v>
+        <v>0.7136</v>
       </c>
       <c r="V8" t="n">
-        <v>1.267</v>
+        <v>-0.3219</v>
       </c>
       <c r="W8" t="n">
-        <v>1.267</v>
+        <v>1.5889</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>-1.9109</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>P. BAENA SÁNCHEZ</t>
+          <t>A. DEMBELE CUESTA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,64 +1111,64 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>1.9005</v>
+        <v>2.2119</v>
       </c>
       <c r="E9" t="n">
-        <v>1.9005</v>
+        <v>1.4651</v>
       </c>
       <c r="F9" t="n">
-        <v>0</v>
+        <v>0.7468</v>
       </c>
       <c r="G9" t="n">
-        <v>1.9005</v>
+        <v>0.6378</v>
       </c>
       <c r="H9" t="n">
-        <v>0.6502</v>
+        <v>0.2564</v>
       </c>
       <c r="I9" t="n">
-        <v>1.2502</v>
+        <v>0.3814</v>
       </c>
       <c r="J9" t="n">
-        <v>1.9005</v>
+        <v>0.125</v>
       </c>
       <c r="K9" t="n">
-        <v>0.6502</v>
+        <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>1.2502</v>
+        <v>0.125</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>0.5128</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>0.2564</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>0.2564</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>0.3665</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>0.3665</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>-0.0594</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>0.0732</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>-0.1325</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>1.267</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.267</v>
       </c>
       <c r="X9" t="n">
         <v>0</v>
@@ -1255,7 +1255,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>P. BAENA SANCHEZ</t>
+          <t>P. BAENA SÁNCHEZ</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,58 +1267,58 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>1.7501</v>
+        <v>1.9005</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.8905</v>
+        <v>1.9005</v>
       </c>
       <c r="F11" t="n">
-        <v>2.6406</v>
+        <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>2.1646</v>
+        <v>1.9005</v>
       </c>
       <c r="H11" t="n">
-        <v>0.0033</v>
+        <v>0.6502</v>
       </c>
       <c r="I11" t="n">
-        <v>2.1613</v>
+        <v>1.2502</v>
       </c>
       <c r="J11" t="n">
-        <v>1.6947</v>
+        <v>1.9005</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.4026</v>
+        <v>0.6502</v>
       </c>
       <c r="L11" t="n">
-        <v>2.0973</v>
+        <v>1.2502</v>
       </c>
       <c r="M11" t="n">
-        <v>0.4698</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>0.4059</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>0.064</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>0.9163</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>-1.8326</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>2.7489</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.3308</v>
+        <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.7526</v>
+        <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.5780999999999999</v>
+        <v>0</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>1.6705</v>
+        <v>1.6209</v>
       </c>
       <c r="E12" t="n">
         <v>0.1823</v>
       </c>
       <c r="F12" t="n">
-        <v>1.4882</v>
+        <v>1.4387</v>
       </c>
       <c r="G12" t="n">
         <v>0.6219</v>
@@ -1390,13 +1390,13 @@
         <v>0.3665</v>
       </c>
       <c r="S12" t="n">
-        <v>0.059</v>
+        <v>0.0094</v>
       </c>
       <c r="T12" t="n">
         <v>0.0732</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.0142</v>
+        <v>-0.06370000000000001</v>
       </c>
       <c r="V12" t="n">
         <v>0.6231</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-1.9837</v>
+        <v>-0.9192</v>
       </c>
       <c r="E14" t="n">
-        <v>-3.5584</v>
+        <v>-3.0637</v>
       </c>
       <c r="F14" t="n">
-        <v>1.5747</v>
+        <v>2.1445</v>
       </c>
       <c r="G14" t="n">
         <v>-0.3649</v>
@@ -1546,13 +1546,13 @@
         <v>2.0158</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.9957</v>
+        <v>0.0688</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.6802</v>
+        <v>-0.1855</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.3155</v>
+        <v>0.2543</v>
       </c>
       <c r="V14" t="n">
         <v>-0.6231</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-2.3876</v>
+        <v>-2.2419</v>
       </c>
       <c r="E15" t="n">
-        <v>-1.4809</v>
+        <v>-1.3848</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.9066</v>
+        <v>-0.8571</v>
       </c>
       <c r="G15" t="n">
         <v>-0.9153</v>
@@ -1624,13 +1624,13 @@
         <v>0.3665</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.5718</v>
+        <v>-0.4261</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.3673</v>
+        <v>-0.2711</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.2045</v>
+        <v>-0.155</v>
       </c>
       <c r="V15" t="n">
         <v>-1.267</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>35.3381</v>
+        <v>35.8887</v>
       </c>
       <c r="E16" t="n">
-        <v>23.5127</v>
+        <v>24.06330000000001</v>
       </c>
       <c r="F16" t="n">
-        <v>11.8256</v>
+        <v>11.8254</v>
       </c>
       <c r="G16" t="n">
         <v>19.36360000000001</v>
@@ -1678,7 +1678,7 @@
         <v>22.2444</v>
       </c>
       <c r="K16" t="n">
-        <v>9.098000000000003</v>
+        <v>9.098000000000001</v>
       </c>
       <c r="L16" t="n">
         <v>13.1461</v>
@@ -1687,7 +1687,7 @@
         <v>-2.880799999999999</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.4742999999999998</v>
+        <v>-0.4743000000000002</v>
       </c>
       <c r="O16" t="n">
         <v>-2.4064</v>
@@ -1702,13 +1702,13 @@
         <v>18.3258</v>
       </c>
       <c r="S16" t="n">
-        <v>0.9163</v>
+        <v>1.4667</v>
       </c>
       <c r="T16" t="n">
-        <v>-1.8511</v>
+        <v>-1.3007</v>
       </c>
       <c r="U16" t="n">
-        <v>2.767599999999999</v>
+        <v>2.767600000000001</v>
       </c>
       <c r="V16" t="n">
         <v>3.1467</v>
@@ -1717,7 +1717,7 @@
         <v>9.5334</v>
       </c>
       <c r="X16" t="n">
-        <v>-6.386999999999999</v>
+        <v>-6.387</v>
       </c>
     </row>
     <row r="17">
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.1039</v>
+        <v>1.6838</v>
       </c>
       <c r="E17" t="n">
-        <v>0.032</v>
+        <v>0.5128</v>
       </c>
       <c r="F17" t="n">
-        <v>1.0719</v>
+        <v>1.171</v>
       </c>
       <c r="G17" t="n">
         <v>0.111</v>
@@ -1780,13 +1780,13 @@
         <v>0.5498</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.3186</v>
+        <v>0.2613</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.5324</v>
+        <v>-0.0516</v>
       </c>
       <c r="U17" t="n">
-        <v>0.2139</v>
+        <v>0.313</v>
       </c>
       <c r="V17" t="n">
         <v>0.945</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.3119</v>
+        <v>0.4329</v>
       </c>
       <c r="E18" t="n">
-        <v>1.8862</v>
+        <v>1.9824</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.5743</v>
+        <v>-1.5495</v>
       </c>
       <c r="G18" t="n">
         <v>1.3762</v>
@@ -1858,13 +1858,13 @@
         <v>0.1833</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.0197</v>
+        <v>0.1012</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.3492</v>
+        <v>-0.253</v>
       </c>
       <c r="U18" t="n">
-        <v>0.3295</v>
+        <v>0.3542</v>
       </c>
       <c r="V18" t="n">
         <v>-0.3115</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.7077</v>
+        <v>-0.2487</v>
       </c>
       <c r="E19" t="n">
-        <v>0.5715</v>
+        <v>0.9560999999999999</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.2791</v>
+        <v>-1.2048</v>
       </c>
       <c r="G19" t="n">
         <v>-1.6026</v>
@@ -1936,13 +1936,13 @@
         <v>0.5498</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.7385</v>
+        <v>-0.2796</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.6606</v>
+        <v>-0.276</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.0779</v>
+        <v>-0.0036</v>
       </c>
       <c r="V19" t="n">
         <v>1.267</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.1934</v>
+        <v>-2.4162</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.4787</v>
+        <v>-2.1518</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.7147</v>
+        <v>-0.2645</v>
       </c>
       <c r="G20" t="n">
         <v>-2.1872</v>
@@ -2014,13 +2014,13 @@
         <v>0.733</v>
       </c>
       <c r="S20" t="n">
-        <v>0.177</v>
+        <v>-0.0458</v>
       </c>
       <c r="T20" t="n">
-        <v>0.8597</v>
+        <v>0.1867</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.6827</v>
+        <v>-0.2325</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.3319</v>
+        <v>-3.448</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.1171</v>
+        <v>-1.8864</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.2148</v>
+        <v>-1.5616</v>
       </c>
       <c r="G21" t="n">
         <v>-2.1769</v>
@@ -2092,13 +2092,13 @@
         <v>0.733</v>
       </c>
       <c r="S21" t="n">
-        <v>1.5101</v>
+        <v>0.394</v>
       </c>
       <c r="T21" t="n">
-        <v>0.6931</v>
+        <v>-0.0761</v>
       </c>
       <c r="U21" t="n">
-        <v>0.8169999999999999</v>
+        <v>0.4702</v>
       </c>
       <c r="V21" t="n">
         <v>1.267</v>
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>D. GONZALEZ FERRER</t>
+          <t>J. ARNAIZ VEGA</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.2137</v>
+        <v>-3.4708</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.8374</v>
+        <v>0.8115</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.3763</v>
+        <v>-4.2823</v>
       </c>
       <c r="G22" t="n">
-        <v>-1.0181</v>
+        <v>-2.8879</v>
       </c>
       <c r="H22" t="n">
-        <v>0.896</v>
+        <v>-0.9136</v>
       </c>
       <c r="I22" t="n">
-        <v>-1.9141</v>
+        <v>-1.9743</v>
       </c>
       <c r="J22" t="n">
-        <v>1.2614</v>
+        <v>0.875</v>
       </c>
       <c r="K22" t="n">
-        <v>1.2197</v>
+        <v>0.8296</v>
       </c>
       <c r="L22" t="n">
-        <v>0.0417</v>
+        <v>0.0455</v>
       </c>
       <c r="M22" t="n">
-        <v>-2.2795</v>
+        <v>-3.7629</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.3237</v>
+        <v>-1.7431</v>
       </c>
       <c r="O22" t="n">
-        <v>-1.9558</v>
+        <v>-2.0198</v>
       </c>
       <c r="P22" t="n">
-        <v>-2.3823</v>
+        <v>0.733</v>
       </c>
       <c r="Q22" t="n">
-        <v>-2.9321</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>0.5498</v>
+        <v>0.733</v>
       </c>
       <c r="S22" t="n">
-        <v>0.8203</v>
+        <v>-0.6929</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.1666</v>
+        <v>-0.7074</v>
       </c>
       <c r="U22" t="n">
-        <v>0.9869</v>
+        <v>0.0145</v>
       </c>
       <c r="V22" t="n">
-        <v>-0.6335</v>
+        <v>-0.6231</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>0.6439</v>
       </c>
       <c r="X22" t="n">
-        <v>-0.6335</v>
+        <v>-1.267</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>J. ARNAIZ VEGA</t>
+          <t>D. GONZALEZ FERRER</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,73 +2203,73 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.8365</v>
+        <v>-3.5066</v>
       </c>
       <c r="E23" t="n">
-        <v>0.6192</v>
+        <v>-1.8374</v>
       </c>
       <c r="F23" t="n">
-        <v>-4.4558</v>
+        <v>-1.6692</v>
       </c>
       <c r="G23" t="n">
-        <v>-2.8879</v>
+        <v>-1.0181</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.9136</v>
+        <v>0.896</v>
       </c>
       <c r="I23" t="n">
-        <v>-1.9743</v>
+        <v>-1.9141</v>
       </c>
       <c r="J23" t="n">
-        <v>0.875</v>
+        <v>1.2614</v>
       </c>
       <c r="K23" t="n">
-        <v>0.8296</v>
+        <v>1.2197</v>
       </c>
       <c r="L23" t="n">
-        <v>0.0455</v>
+        <v>0.0417</v>
       </c>
       <c r="M23" t="n">
-        <v>-3.7629</v>
+        <v>-2.2795</v>
       </c>
       <c r="N23" t="n">
-        <v>-1.7431</v>
+        <v>-0.3237</v>
       </c>
       <c r="O23" t="n">
-        <v>-2.0198</v>
+        <v>-1.9558</v>
       </c>
       <c r="P23" t="n">
-        <v>0.733</v>
+        <v>-2.3823</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>-2.9321</v>
       </c>
       <c r="R23" t="n">
-        <v>0.733</v>
+        <v>0.5498</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.0586</v>
+        <v>0.5273</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.8997000000000001</v>
+        <v>-0.1666</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.1589</v>
+        <v>0.694</v>
       </c>
       <c r="V23" t="n">
-        <v>-0.6231</v>
+        <v>-0.6335</v>
       </c>
       <c r="W23" t="n">
-        <v>0.6439</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>-1.267</v>
+        <v>-0.6335</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>B. FOS CERVERA</t>
+          <t>S. ARNAIZ VEGA</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,73 +2281,73 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-4.3076</v>
+        <v>-3.9572</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.3162</v>
+        <v>-1.2969</v>
       </c>
       <c r="F24" t="n">
-        <v>-3.9914</v>
+        <v>-2.6603</v>
       </c>
       <c r="G24" t="n">
-        <v>-0.4848</v>
+        <v>-2.3982</v>
       </c>
       <c r="H24" t="n">
-        <v>0.2942</v>
+        <v>-0.3883</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.7791</v>
+        <v>-2.0099</v>
       </c>
       <c r="J24" t="n">
-        <v>1.9396</v>
+        <v>-1.0545</v>
       </c>
       <c r="K24" t="n">
-        <v>1.1796</v>
+        <v>-0.0065</v>
       </c>
       <c r="L24" t="n">
-        <v>0.76</v>
+        <v>-1.0479</v>
       </c>
       <c r="M24" t="n">
-        <v>-2.4244</v>
+        <v>-1.3437</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.8854</v>
+        <v>-0.3818</v>
       </c>
       <c r="O24" t="n">
-        <v>-1.5391</v>
+        <v>-0.962</v>
       </c>
       <c r="P24" t="n">
-        <v>-0.1833</v>
+        <v>-0.5498</v>
       </c>
       <c r="Q24" t="n">
-        <v>-0.9163</v>
+        <v>-1.0995</v>
       </c>
       <c r="R24" t="n">
-        <v>0.733</v>
+        <v>0.5498</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.1605</v>
+        <v>-0.3758</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.7164</v>
+        <v>-0.4099</v>
       </c>
       <c r="U24" t="n">
-        <v>0.5558999999999999</v>
+        <v>0.0341</v>
       </c>
       <c r="V24" t="n">
-        <v>-3.479</v>
+        <v>-0.6335</v>
       </c>
       <c r="W24" t="n">
-        <v>-0.6231</v>
+        <v>1.267</v>
       </c>
       <c r="X24" t="n">
-        <v>-2.8559</v>
+        <v>-1.9005</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>S. ARNAIZ VEGA</t>
+          <t>B. FOS CERVERA</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2359,67 +2359,67 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-5.101</v>
+        <v>-4.2843</v>
       </c>
       <c r="E25" t="n">
-        <v>-1.97</v>
+        <v>-0.1239</v>
       </c>
       <c r="F25" t="n">
-        <v>-3.131</v>
+        <v>-4.1604</v>
       </c>
       <c r="G25" t="n">
-        <v>-2.3982</v>
+        <v>-0.4848</v>
       </c>
       <c r="H25" t="n">
-        <v>-0.3883</v>
+        <v>0.2942</v>
       </c>
       <c r="I25" t="n">
-        <v>-2.0099</v>
+        <v>-0.7791</v>
       </c>
       <c r="J25" t="n">
-        <v>-1.0545</v>
+        <v>1.9396</v>
       </c>
       <c r="K25" t="n">
-        <v>-0.0065</v>
+        <v>1.1796</v>
       </c>
       <c r="L25" t="n">
-        <v>-1.0479</v>
+        <v>0.76</v>
       </c>
       <c r="M25" t="n">
-        <v>-1.3437</v>
+        <v>-2.4244</v>
       </c>
       <c r="N25" t="n">
-        <v>-0.3818</v>
+        <v>-0.8854</v>
       </c>
       <c r="O25" t="n">
-        <v>-0.962</v>
+        <v>-1.5391</v>
       </c>
       <c r="P25" t="n">
-        <v>-0.5498</v>
+        <v>-0.1833</v>
       </c>
       <c r="Q25" t="n">
-        <v>-1.0995</v>
+        <v>-0.9163</v>
       </c>
       <c r="R25" t="n">
-        <v>0.5498</v>
+        <v>0.733</v>
       </c>
       <c r="S25" t="n">
-        <v>-1.5195</v>
+        <v>-0.1373</v>
       </c>
       <c r="T25" t="n">
-        <v>-1.0829</v>
+        <v>-0.5241</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.4366</v>
+        <v>0.3869</v>
       </c>
       <c r="V25" t="n">
-        <v>-0.6335</v>
+        <v>-3.479</v>
       </c>
       <c r="W25" t="n">
-        <v>1.267</v>
+        <v>-0.6231</v>
       </c>
       <c r="X25" t="n">
-        <v>-1.9005</v>
+        <v>-2.8559</v>
       </c>
     </row>
     <row r="26">
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-5.5519</v>
+        <v>-5.9818</v>
       </c>
       <c r="E26" t="n">
-        <v>-2.9784</v>
+        <v>-3.363</v>
       </c>
       <c r="F26" t="n">
-        <v>-2.5736</v>
+        <v>-2.6188</v>
       </c>
       <c r="G26" t="n">
         <v>-3.0359</v>
@@ -2482,13 +2482,13 @@
         <v>0.733</v>
       </c>
       <c r="S26" t="n">
-        <v>0.5993000000000001</v>
+        <v>0.1695</v>
       </c>
       <c r="T26" t="n">
-        <v>0.2542</v>
+        <v>-0.1304</v>
       </c>
       <c r="U26" t="n">
-        <v>0.3451</v>
+        <v>0.2999</v>
       </c>
       <c r="V26" t="n">
         <v>0</v>
@@ -2515,13 +2515,13 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>-9.510400000000001</v>
+        <v>-9.5002</v>
       </c>
       <c r="E27" t="n">
-        <v>-5.5586</v>
+        <v>-5.7509</v>
       </c>
       <c r="F27" t="n">
-        <v>-3.9518</v>
+        <v>-3.7492</v>
       </c>
       <c r="G27" t="n">
         <v>-5.0591</v>
@@ -2560,13 +2560,13 @@
         <v>0.3665</v>
       </c>
       <c r="S27" t="n">
-        <v>-0.2076</v>
+        <v>-0.1974</v>
       </c>
       <c r="T27" t="n">
-        <v>-0.1666</v>
+        <v>-0.359</v>
       </c>
       <c r="U27" t="n">
-        <v>-0.041</v>
+        <v>0.1616</v>
       </c>
       <c r="V27" t="n">
         <v>-0.945</v>
@@ -2593,13 +2593,13 @@
         <v>1</v>
       </c>
       <c r="D28" t="n">
-        <v>-35.3383</v>
+        <v>-34.6971</v>
       </c>
       <c r="E28" t="n">
         <v>-12.1475</v>
       </c>
       <c r="F28" t="n">
-        <v>-23.1909</v>
+        <v>-22.5496</v>
       </c>
       <c r="G28" t="n">
         <v>-19.3635</v>
@@ -2611,10 +2611,10 @@
         <v>-10.7397</v>
       </c>
       <c r="J28" t="n">
-        <v>2.880800000000001</v>
+        <v>2.8808</v>
       </c>
       <c r="K28" t="n">
-        <v>0.4745</v>
+        <v>0.4744999999999998</v>
       </c>
       <c r="L28" t="n">
         <v>2.406499999999999</v>
@@ -2638,22 +2638,22 @@
         <v>6.414</v>
       </c>
       <c r="S28" t="n">
-        <v>-0.9163000000000002</v>
+        <v>-0.2755</v>
       </c>
       <c r="T28" t="n">
-        <v>-2.767399999999999</v>
+        <v>-2.7674</v>
       </c>
       <c r="U28" t="n">
-        <v>1.8512</v>
+        <v>2.4923</v>
       </c>
       <c r="V28" t="n">
         <v>-3.1466</v>
       </c>
       <c r="W28" t="n">
-        <v>6.0649</v>
+        <v>6.064900000000001</v>
       </c>
       <c r="X28" t="n">
-        <v>-9.211599999999999</v>
+        <v>-9.211600000000001</v>
       </c>
     </row>
   </sheetData>
